--- a/data/trans_orig/IP16A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32650</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43911</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>45514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33634</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>48667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64032</t>
+          <t>64302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20750</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>34124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>28713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35381</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>50907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>89310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>114590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>75118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>93012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155716</t>
+          <t>154634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181641</t>
+          <t>179914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26364</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52176</t>
+          <t>53770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25385</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37074</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49075</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64767</t>
+          <t>64509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57083</t>
+          <t>57659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38417</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39759</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84067</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102666</t>
+          <t>102194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46443</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36248</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>23445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43993</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64620</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138008</t>
+          <t>138640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97746</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209275</t>
+          <t>207506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>241707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>33495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>45414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>35891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>53169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69375</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35864</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>64080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>35114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28776</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>41536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132584</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89534</t>
+          <t>89902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>83851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>102550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178061</t>
+          <t>178693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206485</t>
+          <t>207254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24282</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,48%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>29298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35798</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53545</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30971</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59809</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>26800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31322</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49058</t>
+          <t>48032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62860</t>
+          <t>61173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72348</t>
+          <t>71850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79789</t>
+          <t>81476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117057</t>
+          <t>119356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>89860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>91778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>171925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134490</t>
+          <t>133859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187232</t>
+          <t>187991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>246380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12023</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7462</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16478</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7954</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12077</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12053</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12023</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7947</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16205</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17632</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13177</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22193</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21081</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16958</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24325</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16982</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24463</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17632</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13450</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21708</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>59,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23461</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17535</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29521</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14295</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9821</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19762</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9744</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19477</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23461</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18132</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28672</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45514</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27499</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21439</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33425</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28926</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23459</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23744</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>33477</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27499</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22288</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>32828</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>53,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48667</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64302</t>
+          <t>63627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8489</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4851</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12107</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6703</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10559</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10803</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8489</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12234</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19015</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15804</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18896</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11704</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18811</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15377</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11632</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19109</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20704</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12343</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7896</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7567</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15370</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10725</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20345</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34124</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24068</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28440</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18200</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13767</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22647</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14123</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22976</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24068</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19093</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28713</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48958</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68940</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33713</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51225</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32833</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>59343</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>50907</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68801</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89310</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114590</t>
+          <t>113480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84576</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74979</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93642</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>84010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>74080</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91592</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>75138</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>92472</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>84576</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75118</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>93012</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154634</t>
+          <t>155744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179914</t>
+          <t>180212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13623</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25808</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24868</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18919</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30644</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30457</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14257</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26334</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>53005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31666</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38126</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24634</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18858</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30583</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19045</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30425</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31666</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25415</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37492</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64509</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -2901,52 +2901,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>49502</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>49502</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>49502</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28521</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21443</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35434</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19933</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25969</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13972</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26578</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>21,41%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28521</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21076</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35986</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38956</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>58249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47382</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54460</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>45314</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39278</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51279</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38669</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>51275</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>59,27%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>78,59%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47382</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>39917</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>54827</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>52,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>132</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83491</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102194</t>
+          <t>101900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>75903</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>75903</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>75903</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>75903</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>75903</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>75903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13467</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9225</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18066</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16742</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11887</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21310</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11875</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21816</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13467</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8757</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18292</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>23675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37767</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19027</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14428</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23269</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20986</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16418</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15912</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25853</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>55,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19027</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14202</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23737</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>46548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13128</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8646</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17719</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17168</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12779</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22306</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>48,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>63,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13128</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9118</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18015</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36578</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19435</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14844</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23917</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>17993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12819</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22382</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12855</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22866</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>51,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19435</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14548</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>23445</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64263</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>86818</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>67251</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>90680</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>66003</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>88793</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>64064</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87054</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138640</t>
+          <t>137731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>170864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>105892</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>128447</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>54,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>108926</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>96957</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>120386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98844</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121634</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>58,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105656</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128646</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207506</t>
+          <t>209483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241707</t>
+          <t>242616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11885</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7376</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16366</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10056</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6438</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14638</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14548</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11885</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8051</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16569</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18294</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13813</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22803</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21237</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16655</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24855</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16745</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25101</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18294</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13610</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22128</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33495</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45414</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30179</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30179</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30179</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30179</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30179</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11281</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21939</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21807</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16031</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27085</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16267</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27297</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>42,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16420</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11475</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21782</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>46238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>30946</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36085</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>30017</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24739</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35793</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24527</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35557</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30946</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>25584</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35891</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53169</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68345</t>
+          <t>68446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51824</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51824</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51824</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11267</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21991</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12756</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17861</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8386</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17770</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11709</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22044</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>36044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26207</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20809</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31533</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31147</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26042</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35844</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26133</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35517</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>26207</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20756</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31091</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>50659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13633</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18553</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13772</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23718</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13732</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23812</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>51,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9255</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13727</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17786</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13408</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21367</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>17686</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22467</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12427</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22507</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>48,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>62,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17786</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13314</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21367</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41536</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,98%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45123</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65094</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53029</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73357</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73578</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>44835</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63534</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>93232</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>82291</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>102262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>100087</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89902</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110230</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>109179</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>55,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>93232</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>83851</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102550</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178693</t>
+          <t>179462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207254</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7523</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8629</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5580</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11506</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7328</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12633</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7354</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4477</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15243</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19997</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15433</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25297</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15769</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>32416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21238</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25802</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24907</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19160</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30854</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25720</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>42706</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19134</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13423</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22793</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17791</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27379</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35288</t>
+          <t>33495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24837</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18926</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30548</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14358</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9772</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19360</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,65%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26089</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25889</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33961</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18378</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32444</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>44745</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61173</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>59579</t>
+          <t>36424</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71850</t>
+          <t>43131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45517</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>67548</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81476</t>
+          <t>58100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119356</t>
+          <t>76727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84667</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43856</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113536</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171925</t>
+          <t>156954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92410</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>80285</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>103241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>106198</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>87855</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>133859</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102105</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>62988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115070</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>208303</t>
+          <t>165758</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187991</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246380</t>
+          <t>179703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
